--- a/Data/Excel/NLFS_II/classification_NLFS_II.xlsx
+++ b/Data/Excel/NLFS_II/classification_NLFS_II.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Sandeep_research\Data\Excel\NLFS_II\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5CA3371-177D-4D50-8431-2230D9FFAE18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8025B6-5B79-4D39-A4AC-D6ED40740EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="caste_II" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="348">
   <si>
     <t>value</t>
   </si>
@@ -393,9 +393,6 @@
     <t>Armed forces occupations</t>
   </si>
   <si>
-    <t>Managers_Professionals_Technicians</t>
-  </si>
-  <si>
     <t>Skill_level_high</t>
   </si>
   <si>
@@ -552,9 +549,6 @@
     <t>Clerical support workers</t>
   </si>
   <si>
-    <t>Clerical_Service_Sales_workers</t>
-  </si>
-  <si>
     <t>Skill_level_medium</t>
   </si>
   <si>
@@ -612,9 +606,6 @@
     <t>Skilled agricultural, forestry and fishery workers</t>
   </si>
   <si>
-    <t>Skilled_agriculture_Trades_workers</t>
-  </si>
-  <si>
     <t>MARKET-ORIENTED ANIMAL PRODUCERS AND RELATED WORKERS</t>
   </si>
   <si>
@@ -891,9 +882,6 @@
     <t>MINING OF COAL AND LIGNITE;EXTRACTION OF PEAT</t>
   </si>
   <si>
-    <t>Mining_quarrying_Electricity_gas_water_supply</t>
-  </si>
-  <si>
     <t>EXTRACTION OF CRUDE PETROLIUM AND NATURAL GAS;SERVICE ACTIVITIES INCIDENTAL TO OIL AND GAS EXTRACTION EXCLUDING..</t>
   </si>
   <si>
@@ -1062,9 +1050,6 @@
     <t>ACTIVITIES OF MEMBERSHIP ORGANIZATIONS N.E.C.</t>
   </si>
   <si>
-    <t>Arts_entertainment_Other_services</t>
-  </si>
-  <si>
     <t>RECREATIONAL, CULTURAL AND SPORTING ACTIVITIES</t>
   </si>
   <si>
@@ -1075,6 +1060,18 @@
   </si>
   <si>
     <t>EXTRA-TERRITORIAL ORGANIZATION AND BODIES</t>
+  </si>
+  <si>
+    <t>Mining_utility</t>
+  </si>
+  <si>
+    <t>Arts_entertain</t>
+  </si>
+  <si>
+    <t>Clerical_sales</t>
+  </si>
+  <si>
+    <t>Agri_trade</t>
   </si>
 </sst>
 </file>
@@ -2944,10 +2941,10 @@
         <v>120</v>
       </c>
       <c r="D2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" t="s">
         <v>121</v>
-      </c>
-      <c r="E2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -2955,16 +2952,16 @@
         <v>111</v>
       </c>
       <c r="B3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" t="s">
         <v>123</v>
       </c>
-      <c r="C3" t="s">
-        <v>124</v>
-      </c>
       <c r="D3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E3" t="s">
         <v>121</v>
-      </c>
-      <c r="E3" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -2972,16 +2969,16 @@
         <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" t="s">
         <v>121</v>
-      </c>
-      <c r="E4" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -2989,16 +2986,16 @@
         <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" t="s">
         <v>121</v>
-      </c>
-      <c r="E5" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -3006,16 +3003,16 @@
         <v>121</v>
       </c>
       <c r="B6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" t="s">
         <v>121</v>
-      </c>
-      <c r="E6" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -3023,16 +3020,16 @@
         <v>122</v>
       </c>
       <c r="B7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" t="s">
         <v>121</v>
-      </c>
-      <c r="E7" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -3040,16 +3037,16 @@
         <v>123</v>
       </c>
       <c r="B8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" t="s">
         <v>121</v>
-      </c>
-      <c r="E8" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -3057,16 +3054,16 @@
         <v>131</v>
       </c>
       <c r="B9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" t="s">
         <v>121</v>
-      </c>
-      <c r="E9" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -3074,16 +3071,16 @@
         <v>211</v>
       </c>
       <c r="B10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" t="s">
         <v>131</v>
       </c>
-      <c r="C10" t="s">
-        <v>132</v>
-      </c>
       <c r="D10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" t="s">
         <v>121</v>
-      </c>
-      <c r="E10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -3091,16 +3088,16 @@
         <v>212</v>
       </c>
       <c r="B11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E11" t="s">
         <v>121</v>
-      </c>
-      <c r="E11" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -3108,16 +3105,16 @@
         <v>213</v>
       </c>
       <c r="B12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" t="s">
         <v>121</v>
-      </c>
-      <c r="E12" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -3125,16 +3122,16 @@
         <v>214</v>
       </c>
       <c r="B13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" t="s">
         <v>121</v>
-      </c>
-      <c r="E13" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -3142,16 +3139,16 @@
         <v>221</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D14" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" t="s">
         <v>121</v>
-      </c>
-      <c r="E14" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -3159,16 +3156,16 @@
         <v>222</v>
       </c>
       <c r="B15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E15" t="s">
         <v>121</v>
-      </c>
-      <c r="E15" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -3176,16 +3173,16 @@
         <v>223</v>
       </c>
       <c r="B16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E16" t="s">
         <v>121</v>
-      </c>
-      <c r="E16" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -3193,16 +3190,16 @@
         <v>231</v>
       </c>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" t="s">
         <v>121</v>
-      </c>
-      <c r="E17" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -3210,16 +3207,16 @@
         <v>232</v>
       </c>
       <c r="B18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D18" t="s">
+        <v>123</v>
+      </c>
+      <c r="E18" t="s">
         <v>121</v>
-      </c>
-      <c r="E18" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -3227,16 +3224,16 @@
         <v>233</v>
       </c>
       <c r="B19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D19" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" t="s">
         <v>121</v>
-      </c>
-      <c r="E19" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -3244,16 +3241,16 @@
         <v>234</v>
       </c>
       <c r="B20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D20" t="s">
+        <v>123</v>
+      </c>
+      <c r="E20" t="s">
         <v>121</v>
-      </c>
-      <c r="E20" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -3261,16 +3258,16 @@
         <v>235</v>
       </c>
       <c r="B21" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D21" t="s">
+        <v>123</v>
+      </c>
+      <c r="E21" t="s">
         <v>121</v>
-      </c>
-      <c r="E21" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -3278,16 +3275,16 @@
         <v>241</v>
       </c>
       <c r="B22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D22" t="s">
+        <v>123</v>
+      </c>
+      <c r="E22" t="s">
         <v>121</v>
-      </c>
-      <c r="E22" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -3295,16 +3292,16 @@
         <v>242</v>
       </c>
       <c r="B23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D23" t="s">
+        <v>123</v>
+      </c>
+      <c r="E23" t="s">
         <v>121</v>
-      </c>
-      <c r="E23" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -3312,16 +3309,16 @@
         <v>243</v>
       </c>
       <c r="B24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D24" t="s">
+        <v>123</v>
+      </c>
+      <c r="E24" t="s">
         <v>121</v>
-      </c>
-      <c r="E24" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -3329,16 +3326,16 @@
         <v>244</v>
       </c>
       <c r="B25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D25" t="s">
+        <v>123</v>
+      </c>
+      <c r="E25" t="s">
         <v>121</v>
-      </c>
-      <c r="E25" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -3346,16 +3343,16 @@
         <v>245</v>
       </c>
       <c r="B26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D26" t="s">
+        <v>123</v>
+      </c>
+      <c r="E26" t="s">
         <v>121</v>
-      </c>
-      <c r="E26" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -3363,16 +3360,16 @@
         <v>246</v>
       </c>
       <c r="B27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D27" t="s">
+        <v>123</v>
+      </c>
+      <c r="E27" t="s">
         <v>121</v>
-      </c>
-      <c r="E27" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -3380,16 +3377,16 @@
         <v>311</v>
       </c>
       <c r="B28" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" t="s">
         <v>150</v>
       </c>
-      <c r="C28" t="s">
-        <v>151</v>
-      </c>
       <c r="D28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" t="s">
         <v>121</v>
-      </c>
-      <c r="E28" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -3397,16 +3394,16 @@
         <v>312</v>
       </c>
       <c r="B29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D29" t="s">
+        <v>123</v>
+      </c>
+      <c r="E29" t="s">
         <v>121</v>
-      </c>
-      <c r="E29" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -3414,16 +3411,16 @@
         <v>313</v>
       </c>
       <c r="B30" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D30" t="s">
+        <v>123</v>
+      </c>
+      <c r="E30" t="s">
         <v>121</v>
-      </c>
-      <c r="E30" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -3431,16 +3428,16 @@
         <v>314</v>
       </c>
       <c r="B31" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D31" t="s">
+        <v>123</v>
+      </c>
+      <c r="E31" t="s">
         <v>121</v>
-      </c>
-      <c r="E31" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -3448,16 +3445,16 @@
         <v>315</v>
       </c>
       <c r="B32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D32" t="s">
+        <v>123</v>
+      </c>
+      <c r="E32" t="s">
         <v>121</v>
-      </c>
-      <c r="E32" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -3465,16 +3462,16 @@
         <v>321</v>
       </c>
       <c r="B33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D33" t="s">
+        <v>123</v>
+      </c>
+      <c r="E33" t="s">
         <v>121</v>
-      </c>
-      <c r="E33" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -3482,16 +3479,16 @@
         <v>322</v>
       </c>
       <c r="B34" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D34" t="s">
+        <v>123</v>
+      </c>
+      <c r="E34" t="s">
         <v>121</v>
-      </c>
-      <c r="E34" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -3499,16 +3496,16 @@
         <v>323</v>
       </c>
       <c r="B35" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D35" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" t="s">
         <v>121</v>
-      </c>
-      <c r="E35" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -3516,16 +3513,16 @@
         <v>324</v>
       </c>
       <c r="B36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D36" t="s">
+        <v>123</v>
+      </c>
+      <c r="E36" t="s">
         <v>121</v>
-      </c>
-      <c r="E36" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -3533,16 +3530,16 @@
         <v>331</v>
       </c>
       <c r="B37" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D37" t="s">
+        <v>123</v>
+      </c>
+      <c r="E37" t="s">
         <v>121</v>
-      </c>
-      <c r="E37" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
@@ -3550,16 +3547,16 @@
         <v>332</v>
       </c>
       <c r="B38" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D38" t="s">
+        <v>123</v>
+      </c>
+      <c r="E38" t="s">
         <v>121</v>
-      </c>
-      <c r="E38" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -3567,16 +3564,16 @@
         <v>333</v>
       </c>
       <c r="B39" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C39" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D39" t="s">
+        <v>123</v>
+      </c>
+      <c r="E39" t="s">
         <v>121</v>
-      </c>
-      <c r="E39" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -3584,16 +3581,16 @@
         <v>334</v>
       </c>
       <c r="B40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D40" t="s">
+        <v>123</v>
+      </c>
+      <c r="E40" t="s">
         <v>121</v>
-      </c>
-      <c r="E40" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
@@ -3601,16 +3598,16 @@
         <v>341</v>
       </c>
       <c r="B41" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C41" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D41" t="s">
+        <v>123</v>
+      </c>
+      <c r="E41" t="s">
         <v>121</v>
-      </c>
-      <c r="E41" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
@@ -3618,16 +3615,16 @@
         <v>342</v>
       </c>
       <c r="B42" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D42" t="s">
+        <v>123</v>
+      </c>
+      <c r="E42" t="s">
         <v>121</v>
-      </c>
-      <c r="E42" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -3635,16 +3632,16 @@
         <v>343</v>
       </c>
       <c r="B43" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C43" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D43" t="s">
+        <v>123</v>
+      </c>
+      <c r="E43" t="s">
         <v>121</v>
-      </c>
-      <c r="E43" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
@@ -3652,16 +3649,16 @@
         <v>344</v>
       </c>
       <c r="B44" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C44" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D44" t="s">
+        <v>123</v>
+      </c>
+      <c r="E44" t="s">
         <v>121</v>
-      </c>
-      <c r="E44" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
@@ -3669,16 +3666,16 @@
         <v>345</v>
       </c>
       <c r="B45" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C45" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D45" t="s">
+        <v>123</v>
+      </c>
+      <c r="E45" t="s">
         <v>121</v>
-      </c>
-      <c r="E45" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
@@ -3686,16 +3683,16 @@
         <v>346</v>
       </c>
       <c r="B46" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C46" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D46" t="s">
+        <v>123</v>
+      </c>
+      <c r="E46" t="s">
         <v>121</v>
-      </c>
-      <c r="E46" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
@@ -3703,16 +3700,16 @@
         <v>347</v>
       </c>
       <c r="B47" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C47" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D47" t="s">
+        <v>123</v>
+      </c>
+      <c r="E47" t="s">
         <v>121</v>
-      </c>
-      <c r="E47" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
@@ -3720,16 +3717,16 @@
         <v>348</v>
       </c>
       <c r="B48" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C48" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D48" t="s">
+        <v>123</v>
+      </c>
+      <c r="E48" t="s">
         <v>121</v>
-      </c>
-      <c r="E48" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
@@ -3737,16 +3734,16 @@
         <v>411</v>
       </c>
       <c r="B49" t="s">
+        <v>171</v>
+      </c>
+      <c r="C49" t="s">
         <v>172</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
+        <v>346</v>
+      </c>
+      <c r="E49" t="s">
         <v>173</v>
-      </c>
-      <c r="D49" t="s">
-        <v>174</v>
-      </c>
-      <c r="E49" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
@@ -3754,16 +3751,16 @@
         <v>412</v>
       </c>
       <c r="B50" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C50" t="s">
+        <v>172</v>
+      </c>
+      <c r="D50" t="s">
+        <v>346</v>
+      </c>
+      <c r="E50" t="s">
         <v>173</v>
-      </c>
-      <c r="D50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E50" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
@@ -3771,16 +3768,16 @@
         <v>413</v>
       </c>
       <c r="B51" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C51" t="s">
+        <v>172</v>
+      </c>
+      <c r="D51" t="s">
+        <v>346</v>
+      </c>
+      <c r="E51" t="s">
         <v>173</v>
-      </c>
-      <c r="D51" t="s">
-        <v>174</v>
-      </c>
-      <c r="E51" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
@@ -3788,16 +3785,16 @@
         <v>414</v>
       </c>
       <c r="B52" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C52" t="s">
+        <v>172</v>
+      </c>
+      <c r="D52" t="s">
+        <v>346</v>
+      </c>
+      <c r="E52" t="s">
         <v>173</v>
-      </c>
-      <c r="D52" t="s">
-        <v>174</v>
-      </c>
-      <c r="E52" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
@@ -3805,16 +3802,16 @@
         <v>419</v>
       </c>
       <c r="B53" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C53" t="s">
+        <v>172</v>
+      </c>
+      <c r="D53" t="s">
+        <v>346</v>
+      </c>
+      <c r="E53" t="s">
         <v>173</v>
-      </c>
-      <c r="D53" t="s">
-        <v>174</v>
-      </c>
-      <c r="E53" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
@@ -3822,16 +3819,16 @@
         <v>421</v>
       </c>
       <c r="B54" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C54" t="s">
+        <v>172</v>
+      </c>
+      <c r="D54" t="s">
+        <v>346</v>
+      </c>
+      <c r="E54" t="s">
         <v>173</v>
-      </c>
-      <c r="D54" t="s">
-        <v>174</v>
-      </c>
-      <c r="E54" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
@@ -3839,16 +3836,16 @@
         <v>422</v>
       </c>
       <c r="B55" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C55" t="s">
+        <v>172</v>
+      </c>
+      <c r="D55" t="s">
+        <v>346</v>
+      </c>
+      <c r="E55" t="s">
         <v>173</v>
-      </c>
-      <c r="D55" t="s">
-        <v>174</v>
-      </c>
-      <c r="E55" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
@@ -3856,16 +3853,16 @@
         <v>511</v>
       </c>
       <c r="B56" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C56" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D56" t="s">
-        <v>174</v>
+        <v>346</v>
       </c>
       <c r="E56" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
@@ -3873,16 +3870,16 @@
         <v>512</v>
       </c>
       <c r="B57" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C57" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D57" t="s">
-        <v>174</v>
+        <v>346</v>
       </c>
       <c r="E57" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
@@ -3890,16 +3887,16 @@
         <v>513</v>
       </c>
       <c r="B58" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C58" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D58" t="s">
-        <v>174</v>
+        <v>346</v>
       </c>
       <c r="E58" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
@@ -3907,16 +3904,16 @@
         <v>514</v>
       </c>
       <c r="B59" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C59" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D59" t="s">
-        <v>174</v>
+        <v>346</v>
       </c>
       <c r="E59" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
@@ -3924,16 +3921,16 @@
         <v>515</v>
       </c>
       <c r="B60" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C60" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D60" t="s">
-        <v>174</v>
+        <v>346</v>
       </c>
       <c r="E60" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
@@ -3941,16 +3938,16 @@
         <v>516</v>
       </c>
       <c r="B61" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C61" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D61" t="s">
-        <v>174</v>
+        <v>346</v>
       </c>
       <c r="E61" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
@@ -3958,16 +3955,16 @@
         <v>521</v>
       </c>
       <c r="B62" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C62" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D62" t="s">
-        <v>174</v>
+        <v>346</v>
       </c>
       <c r="E62" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
@@ -3975,16 +3972,16 @@
         <v>522</v>
       </c>
       <c r="B63" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C63" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D63" t="s">
-        <v>174</v>
+        <v>346</v>
       </c>
       <c r="E63" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
@@ -3992,16 +3989,16 @@
         <v>523</v>
       </c>
       <c r="B64" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C64" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D64" t="s">
-        <v>174</v>
+        <v>346</v>
       </c>
       <c r="E64" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
@@ -4009,16 +4006,16 @@
         <v>611</v>
       </c>
       <c r="B65" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C65" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D65" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E65" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
@@ -4026,16 +4023,16 @@
         <v>612</v>
       </c>
       <c r="B66" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C66" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D66" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E66" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
@@ -4043,16 +4040,16 @@
         <v>613</v>
       </c>
       <c r="B67" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C67" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D67" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E67" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
@@ -4060,16 +4057,16 @@
         <v>614</v>
       </c>
       <c r="B68" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C68" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D68" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E68" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
@@ -4077,16 +4074,16 @@
         <v>615</v>
       </c>
       <c r="B69" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C69" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D69" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E69" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
@@ -4094,16 +4091,16 @@
         <v>621</v>
       </c>
       <c r="B70" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C70" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D70" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E70" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
@@ -4111,16 +4108,16 @@
         <v>711</v>
       </c>
       <c r="B71" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C71" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D71" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E71" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
@@ -4128,16 +4125,16 @@
         <v>712</v>
       </c>
       <c r="B72" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C72" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D72" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E72" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
@@ -4145,16 +4142,16 @@
         <v>713</v>
       </c>
       <c r="B73" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C73" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D73" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E73" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
@@ -4162,16 +4159,16 @@
         <v>714</v>
       </c>
       <c r="B74" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C74" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D74" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E74" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
@@ -4179,16 +4176,16 @@
         <v>721</v>
       </c>
       <c r="B75" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C75" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D75" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E75" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
@@ -4196,16 +4193,16 @@
         <v>722</v>
       </c>
       <c r="B76" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C76" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D76" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E76" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
@@ -4213,16 +4210,16 @@
         <v>723</v>
       </c>
       <c r="B77" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C77" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D77" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E77" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
@@ -4230,16 +4227,16 @@
         <v>724</v>
       </c>
       <c r="B78" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C78" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D78" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E78" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
@@ -4247,16 +4244,16 @@
         <v>731</v>
       </c>
       <c r="B79" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C79" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D79" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E79" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
@@ -4264,16 +4261,16 @@
         <v>732</v>
       </c>
       <c r="B80" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C80" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D80" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E80" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
@@ -4281,16 +4278,16 @@
         <v>733</v>
       </c>
       <c r="B81" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C81" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D81" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E81" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
@@ -4298,16 +4295,16 @@
         <v>734</v>
       </c>
       <c r="B82" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C82" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D82" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E82" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
@@ -4315,16 +4312,16 @@
         <v>741</v>
       </c>
       <c r="B83" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C83" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D83" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E83" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
@@ -4332,16 +4329,16 @@
         <v>742</v>
       </c>
       <c r="B84" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C84" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D84" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E84" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
@@ -4349,16 +4346,16 @@
         <v>743</v>
       </c>
       <c r="B85" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C85" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D85" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E85" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
@@ -4366,16 +4363,16 @@
         <v>744</v>
       </c>
       <c r="B86" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C86" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D86" t="s">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="E86" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
@@ -4383,16 +4380,16 @@
         <v>811</v>
       </c>
       <c r="B87" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C87" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D87" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E87" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
@@ -4400,16 +4397,16 @@
         <v>812</v>
       </c>
       <c r="B88" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C88" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D88" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E88" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
@@ -4417,16 +4414,16 @@
         <v>813</v>
       </c>
       <c r="B89" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C89" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D89" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E89" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
@@ -4434,16 +4431,16 @@
         <v>814</v>
       </c>
       <c r="B90" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C90" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D90" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E90" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
@@ -4451,16 +4448,16 @@
         <v>815</v>
       </c>
       <c r="B91" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C91" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D91" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E91" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
@@ -4468,16 +4465,16 @@
         <v>816</v>
       </c>
       <c r="B92" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C92" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D92" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E92" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
@@ -4485,16 +4482,16 @@
         <v>817</v>
       </c>
       <c r="B93" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C93" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D93" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E93" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
@@ -4502,16 +4499,16 @@
         <v>821</v>
       </c>
       <c r="B94" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C94" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D94" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E94" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
@@ -4519,16 +4516,16 @@
         <v>822</v>
       </c>
       <c r="B95" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C95" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D95" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E95" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
@@ -4536,16 +4533,16 @@
         <v>823</v>
       </c>
       <c r="B96" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C96" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D96" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E96" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
@@ -4553,16 +4550,16 @@
         <v>824</v>
       </c>
       <c r="B97" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D97" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E97" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
@@ -4570,16 +4567,16 @@
         <v>825</v>
       </c>
       <c r="B98" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C98" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D98" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E98" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
@@ -4587,16 +4584,16 @@
         <v>826</v>
       </c>
       <c r="B99" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C99" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D99" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E99" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
@@ -4604,16 +4601,16 @@
         <v>827</v>
       </c>
       <c r="B100" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C100" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D100" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E100" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
@@ -4621,16 +4618,16 @@
         <v>828</v>
       </c>
       <c r="B101" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C101" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D101" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E101" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
@@ -4638,16 +4635,16 @@
         <v>829</v>
       </c>
       <c r="B102" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C102" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D102" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E102" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
@@ -4655,16 +4652,16 @@
         <v>831</v>
       </c>
       <c r="B103" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C103" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D103" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E103" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
@@ -4672,16 +4669,16 @@
         <v>832</v>
       </c>
       <c r="B104" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C104" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D104" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E104" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
@@ -4689,16 +4686,16 @@
         <v>833</v>
       </c>
       <c r="B105" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C105" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D105" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E105" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
@@ -4706,16 +4703,16 @@
         <v>911</v>
       </c>
       <c r="B106" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C106" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D106" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E106" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
@@ -4723,16 +4720,16 @@
         <v>912</v>
       </c>
       <c r="B107" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C107" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D107" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E107" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
@@ -4740,16 +4737,16 @@
         <v>913</v>
       </c>
       <c r="B108" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C108" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D108" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E108" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
@@ -4757,16 +4754,16 @@
         <v>914</v>
       </c>
       <c r="B109" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C109" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D109" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E109" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
@@ -4774,16 +4771,16 @@
         <v>915</v>
       </c>
       <c r="B110" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C110" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D110" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E110" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
@@ -4791,16 +4788,16 @@
         <v>916</v>
       </c>
       <c r="B111" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C111" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D111" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E111" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
@@ -4808,16 +4805,16 @@
         <v>921</v>
       </c>
       <c r="B112" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C112" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D112" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E112" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
@@ -4825,16 +4822,16 @@
         <v>931</v>
       </c>
       <c r="B113" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C113" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D113" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E113" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
@@ -4842,16 +4839,16 @@
         <v>932</v>
       </c>
       <c r="B114" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C114" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D114" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E114" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
@@ -4859,16 +4856,16 @@
         <v>933</v>
       </c>
       <c r="B115" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C115" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D115" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E115" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
@@ -4876,16 +4873,16 @@
         <v>996</v>
       </c>
       <c r="B116" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C116" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D116" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E116" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
@@ -4893,16 +4890,16 @@
         <v>997</v>
       </c>
       <c r="B117" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C117" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D117" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E117" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
@@ -4910,16 +4907,16 @@
         <v>998</v>
       </c>
       <c r="B118" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C118" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D118" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E118" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
@@ -4927,16 +4924,16 @@
         <v>999</v>
       </c>
       <c r="B119" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C119" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D119" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E119" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -4965,10 +4962,10 @@
         <v>115</v>
       </c>
       <c r="C1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -4976,10 +4973,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -4990,10 +4987,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -5004,10 +5001,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -5018,10 +5015,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -5032,10 +5029,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -5046,10 +5043,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C7" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -5060,10 +5057,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C8" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -5074,10 +5071,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C9" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -5088,10 +5085,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C10" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -5102,10 +5099,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C11" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -5116,10 +5113,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C12" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -5130,10 +5127,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C13" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D13">
         <v>11</v>
@@ -5144,10 +5141,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C14" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -5158,10 +5155,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C15" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D15">
         <v>17</v>
@@ -5172,10 +5169,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C16" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D16">
         <v>19</v>
@@ -5186,10 +5183,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C17" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D17">
         <v>13</v>
@@ -5200,10 +5197,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C18" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -5214,10 +5211,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C19" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -5228,10 +5225,10 @@
         <v>99</v>
       </c>
       <c r="B20" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C20" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -5263,7 +5260,7 @@
         <v>115</v>
       </c>
       <c r="C1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -5271,10 +5268,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -5282,10 +5279,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C3" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -5293,10 +5290,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -5304,10 +5301,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C5" t="s">
-        <v>287</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -5315,10 +5312,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C6" t="s">
-        <v>287</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -5326,10 +5323,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C7" t="s">
-        <v>287</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -5337,10 +5334,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C8" t="s">
-        <v>287</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -5348,10 +5345,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C9" t="s">
-        <v>287</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -5359,10 +5356,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C10" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -5370,10 +5367,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C11" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -5381,10 +5378,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C12" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -5392,10 +5389,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C13" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -5403,10 +5400,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C14" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -5414,10 +5411,10 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C15" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -5425,10 +5422,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C16" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -5436,10 +5433,10 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C17" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -5447,10 +5444,10 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C18" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
@@ -5458,10 +5455,10 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C19" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -5469,10 +5466,10 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C20" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -5480,10 +5477,10 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C21" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -5491,10 +5488,10 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C22" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -5502,10 +5499,10 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C23" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -5513,10 +5510,10 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C24" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -5524,10 +5521,10 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C25" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -5535,10 +5532,10 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C26" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -5546,10 +5543,10 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C27" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
@@ -5557,10 +5554,10 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C28" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
@@ -5568,10 +5565,10 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C29" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -5579,10 +5576,10 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C30" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
@@ -5590,10 +5587,10 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C31" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
@@ -5601,10 +5598,10 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C32" t="s">
-        <v>287</v>
+        <v>344</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
@@ -5612,10 +5609,10 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C33" t="s">
-        <v>287</v>
+        <v>344</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
@@ -5623,10 +5620,10 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C34" t="s">
-        <v>287</v>
+        <v>344</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
@@ -5634,10 +5631,10 @@
         <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C35" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
@@ -5645,10 +5642,10 @@
         <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C36" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
@@ -5656,10 +5653,10 @@
         <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C37" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
@@ -5667,10 +5664,10 @@
         <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C38" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
@@ -5678,10 +5675,10 @@
         <v>55</v>
       </c>
       <c r="B39" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C39" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
@@ -5689,10 +5686,10 @@
         <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C40" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
@@ -5700,10 +5697,10 @@
         <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C41" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
@@ -5711,10 +5708,10 @@
         <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C42" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
@@ -5722,10 +5719,10 @@
         <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C43" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
@@ -5733,10 +5730,10 @@
         <v>64</v>
       </c>
       <c r="B44" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C44" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
@@ -5744,10 +5741,10 @@
         <v>65</v>
       </c>
       <c r="B45" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C45" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
@@ -5755,10 +5752,10 @@
         <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C46" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
@@ -5766,10 +5763,10 @@
         <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C47" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
@@ -5777,10 +5774,10 @@
         <v>70</v>
       </c>
       <c r="B48" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C48" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
@@ -5788,10 +5785,10 @@
         <v>71</v>
       </c>
       <c r="B49" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C49" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
@@ -5799,10 +5796,10 @@
         <v>72</v>
       </c>
       <c r="B50" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C50" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
@@ -5810,10 +5807,10 @@
         <v>73</v>
       </c>
       <c r="B51" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C51" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
@@ -5821,10 +5818,10 @@
         <v>74</v>
       </c>
       <c r="B52" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C52" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
@@ -5832,10 +5829,10 @@
         <v>75</v>
       </c>
       <c r="B53" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C53" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
@@ -5843,10 +5840,10 @@
         <v>80</v>
       </c>
       <c r="B54" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C54" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
@@ -5854,10 +5851,10 @@
         <v>85</v>
       </c>
       <c r="B55" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C55" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
@@ -5865,10 +5862,10 @@
         <v>90</v>
       </c>
       <c r="B56" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C56" t="s">
-        <v>287</v>
+        <v>344</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
@@ -5876,10 +5873,10 @@
         <v>91</v>
       </c>
       <c r="B57" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C57" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
@@ -5887,10 +5884,10 @@
         <v>92</v>
       </c>
       <c r="B58" t="s">
+        <v>340</v>
+      </c>
+      <c r="C58" t="s">
         <v>345</v>
-      </c>
-      <c r="C58" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
@@ -5898,10 +5895,10 @@
         <v>93</v>
       </c>
       <c r="B59" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C59" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
@@ -5909,10 +5906,10 @@
         <v>95</v>
       </c>
       <c r="B60" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C60" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
@@ -5920,10 +5917,10 @@
         <v>99</v>
       </c>
       <c r="B61" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C61" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Excel/NLFS_II/classification_NLFS_II.xlsx
+++ b/Data/Excel/NLFS_II/classification_NLFS_II.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Sandeep_research\Data\Excel\NLFS_II\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Formal_Informal_wage\Data\Excel\NLFS_II\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8025B6-5B79-4D39-A4AC-D6ED40740EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B77DF3-0E9F-4414-8FA2-601703785223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="349">
   <si>
     <t>value</t>
   </si>
@@ -1072,6 +1072,9 @@
   </si>
   <si>
     <t>Agri_trade</t>
+  </si>
+  <si>
+    <t>two_digit</t>
   </si>
 </sst>
 </file>
@@ -2904,2035 +2907,2392 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr defaultColWidth="11.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="74.26953125" customWidth="1"/>
-    <col min="3" max="3" width="35.7265625" customWidth="1"/>
-    <col min="4" max="4" width="38.453125" customWidth="1"/>
-    <col min="5" max="5" width="20.7265625" customWidth="1"/>
+    <col min="3" max="3" width="74.26953125" customWidth="1"/>
+    <col min="4" max="4" width="35.7265625" customWidth="1"/>
+    <col min="5" max="5" width="38.453125" customWidth="1"/>
+    <col min="6" max="6" width="20.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C1" t="s">
         <v>115</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>116</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>117</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
         <v>119</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>120</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>123</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>111</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>122</v>
-      </c>
-      <c r="C3" t="s">
-        <v>123</v>
       </c>
       <c r="D3" t="s">
         <v>123</v>
       </c>
       <c r="E3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>112</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>124</v>
-      </c>
-      <c r="C4" t="s">
-        <v>123</v>
       </c>
       <c r="D4" t="s">
         <v>123</v>
       </c>
       <c r="E4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>114</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
         <v>125</v>
-      </c>
-      <c r="C5" t="s">
-        <v>123</v>
       </c>
       <c r="D5" t="s">
         <v>123</v>
       </c>
       <c r="E5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F5" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>121</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
         <v>126</v>
-      </c>
-      <c r="C6" t="s">
-        <v>123</v>
       </c>
       <c r="D6" t="s">
         <v>123</v>
       </c>
       <c r="E6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>122</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
         <v>127</v>
-      </c>
-      <c r="C7" t="s">
-        <v>123</v>
       </c>
       <c r="D7" t="s">
         <v>123</v>
       </c>
       <c r="E7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>123</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
         <v>128</v>
-      </c>
-      <c r="C8" t="s">
-        <v>123</v>
       </c>
       <c r="D8" t="s">
         <v>123</v>
       </c>
       <c r="E8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>131</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
         <v>129</v>
-      </c>
-      <c r="C9" t="s">
-        <v>123</v>
       </c>
       <c r="D9" t="s">
         <v>123</v>
       </c>
       <c r="E9" t="s">
+        <v>123</v>
+      </c>
+      <c r="F9" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>211</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
         <v>130</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>131</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>123</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>212</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
         <v>132</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>131</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>123</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>213</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
         <v>133</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>131</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>123</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>214</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
         <v>134</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>131</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>123</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>221</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
         <v>135</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>131</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>123</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>222</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
         <v>136</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>131</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>123</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>223</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
         <v>137</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>131</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>123</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>231</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
         <v>138</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>131</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>123</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>232</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
         <v>139</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>131</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>123</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>233</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
         <v>140</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>131</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>123</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>234</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20">
+        <v>23</v>
+      </c>
+      <c r="C20" t="s">
         <v>141</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>131</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>123</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>235</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21">
+        <v>23</v>
+      </c>
+      <c r="C21" t="s">
         <v>142</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>131</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>123</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>241</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
         <v>143</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>131</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>123</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>242</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
         <v>144</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>131</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>123</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>243</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
         <v>145</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>131</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>123</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>244</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
         <v>146</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>131</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>123</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>245</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26">
+        <v>24</v>
+      </c>
+      <c r="C26" t="s">
         <v>147</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>131</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>123</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>246</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
         <v>148</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>131</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>123</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>311</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28">
+        <v>31</v>
+      </c>
+      <c r="C28" t="s">
         <v>149</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>150</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>123</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>312</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29">
+        <v>31</v>
+      </c>
+      <c r="C29" t="s">
         <v>151</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>150</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>123</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>313</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30">
+        <v>31</v>
+      </c>
+      <c r="C30" t="s">
         <v>152</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>150</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>123</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>314</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31">
+        <v>31</v>
+      </c>
+      <c r="C31" t="s">
         <v>153</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>150</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>123</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>315</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32">
+        <v>31</v>
+      </c>
+      <c r="C32" t="s">
         <v>154</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>150</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>123</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>321</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
         <v>155</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>150</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>123</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>322</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34">
+        <v>32</v>
+      </c>
+      <c r="C34" t="s">
         <v>156</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>150</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>123</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>323</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35">
+        <v>32</v>
+      </c>
+      <c r="C35" t="s">
         <v>157</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>150</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>123</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>324</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36">
+        <v>32</v>
+      </c>
+      <c r="C36" t="s">
         <v>158</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>150</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>123</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>331</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37">
+        <v>33</v>
+      </c>
+      <c r="C37" t="s">
         <v>159</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>150</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>123</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>332</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38">
+        <v>33</v>
+      </c>
+      <c r="C38" t="s">
         <v>160</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>150</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>123</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>333</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39">
+        <v>33</v>
+      </c>
+      <c r="C39" t="s">
         <v>161</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>150</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>123</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>334</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40">
+        <v>33</v>
+      </c>
+      <c r="C40" t="s">
         <v>162</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>150</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>123</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>341</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41">
+        <v>34</v>
+      </c>
+      <c r="C41" t="s">
         <v>163</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>150</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>123</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>342</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42">
+        <v>34</v>
+      </c>
+      <c r="C42" t="s">
         <v>164</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>150</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>123</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>343</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43">
+        <v>34</v>
+      </c>
+      <c r="C43" t="s">
         <v>165</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>150</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>123</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>344</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44">
+        <v>34</v>
+      </c>
+      <c r="C44" t="s">
         <v>166</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>150</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>123</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>345</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45">
+        <v>34</v>
+      </c>
+      <c r="C45" t="s">
         <v>167</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>150</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>123</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>346</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46">
+        <v>34</v>
+      </c>
+      <c r="C46" t="s">
         <v>168</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>150</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>123</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>347</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47">
+        <v>34</v>
+      </c>
+      <c r="C47" t="s">
         <v>169</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>150</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>123</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>348</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48">
+        <v>34</v>
+      </c>
+      <c r="C48" t="s">
         <v>170</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>150</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>123</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>411</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49">
+        <v>41</v>
+      </c>
+      <c r="C49" t="s">
         <v>171</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>172</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>346</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>412</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50">
+        <v>41</v>
+      </c>
+      <c r="C50" t="s">
         <v>174</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>172</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>346</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>413</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51">
+        <v>41</v>
+      </c>
+      <c r="C51" t="s">
         <v>175</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>172</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>346</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>414</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52">
+        <v>41</v>
+      </c>
+      <c r="C52" t="s">
         <v>176</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>172</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>346</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>419</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53">
+        <v>41</v>
+      </c>
+      <c r="C53" t="s">
         <v>177</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>172</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>346</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>421</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54">
+        <v>42</v>
+      </c>
+      <c r="C54" t="s">
         <v>178</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>172</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>346</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>422</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55">
+        <v>42</v>
+      </c>
+      <c r="C55" t="s">
         <v>179</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>172</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>346</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>511</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56">
+        <v>51</v>
+      </c>
+      <c r="C56" t="s">
         <v>180</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>181</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>346</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>512</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57">
+        <v>51</v>
+      </c>
+      <c r="C57" t="s">
         <v>182</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>181</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>346</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>513</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58">
+        <v>51</v>
+      </c>
+      <c r="C58" t="s">
         <v>183</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>181</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>346</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>514</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59">
+        <v>51</v>
+      </c>
+      <c r="C59" t="s">
         <v>184</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>181</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>346</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>515</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60">
+        <v>51</v>
+      </c>
+      <c r="C60" t="s">
         <v>185</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>181</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>346</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>516</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61">
+        <v>51</v>
+      </c>
+      <c r="C61" t="s">
         <v>186</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>181</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>346</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>521</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62">
+        <v>52</v>
+      </c>
+      <c r="C62" t="s">
         <v>187</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>181</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>346</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>522</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63">
+        <v>52</v>
+      </c>
+      <c r="C63" t="s">
         <v>188</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>181</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>346</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>523</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64">
+        <v>52</v>
+      </c>
+      <c r="C64" t="s">
         <v>189</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>181</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>346</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>611</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65">
+        <v>61</v>
+      </c>
+      <c r="C65" t="s">
         <v>190</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>191</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>347</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>612</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66">
+        <v>61</v>
+      </c>
+      <c r="C66" t="s">
         <v>192</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>191</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>347</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>613</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67">
+        <v>61</v>
+      </c>
+      <c r="C67" t="s">
         <v>193</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>191</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>347</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>614</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68">
+        <v>61</v>
+      </c>
+      <c r="C68" t="s">
         <v>194</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>191</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>347</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>615</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69">
+        <v>61</v>
+      </c>
+      <c r="C69" t="s">
         <v>195</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>191</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>347</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>621</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70">
+        <v>62</v>
+      </c>
+      <c r="C70" t="s">
         <v>196</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>191</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>347</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>711</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71">
+        <v>71</v>
+      </c>
+      <c r="C71" t="s">
         <v>197</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>198</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>347</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>712</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72">
+        <v>71</v>
+      </c>
+      <c r="C72" t="s">
         <v>199</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>198</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>347</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>713</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73">
+        <v>71</v>
+      </c>
+      <c r="C73" t="s">
         <v>200</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
         <v>198</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>347</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>714</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74">
+        <v>71</v>
+      </c>
+      <c r="C74" t="s">
         <v>201</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
         <v>198</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>347</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>721</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75">
+        <v>72</v>
+      </c>
+      <c r="C75" t="s">
         <v>202</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
         <v>198</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>347</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>722</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76">
+        <v>72</v>
+      </c>
+      <c r="C76" t="s">
         <v>203</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>198</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>347</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>723</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77">
+        <v>72</v>
+      </c>
+      <c r="C77" t="s">
         <v>204</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>198</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>347</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>724</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78">
+        <v>72</v>
+      </c>
+      <c r="C78" t="s">
         <v>205</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>198</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>347</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>731</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79">
+        <v>73</v>
+      </c>
+      <c r="C79" t="s">
         <v>206</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
         <v>198</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>347</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>732</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80">
+        <v>73</v>
+      </c>
+      <c r="C80" t="s">
         <v>207</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>198</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>347</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>733</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81">
+        <v>73</v>
+      </c>
+      <c r="C81" t="s">
         <v>208</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D81" t="s">
         <v>198</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
         <v>347</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>734</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82">
+        <v>73</v>
+      </c>
+      <c r="C82" t="s">
         <v>209</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="s">
         <v>198</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>347</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>741</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83">
+        <v>74</v>
+      </c>
+      <c r="C83" t="s">
         <v>210</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
         <v>198</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>347</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>742</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84">
+        <v>74</v>
+      </c>
+      <c r="C84" t="s">
         <v>211</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>198</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>347</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>743</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85">
+        <v>74</v>
+      </c>
+      <c r="C85" t="s">
         <v>212</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
         <v>198</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
         <v>347</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>744</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86">
+        <v>74</v>
+      </c>
+      <c r="C86" t="s">
         <v>213</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
         <v>198</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>347</v>
       </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>811</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87">
+        <v>81</v>
+      </c>
+      <c r="C87" t="s">
         <v>214</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
         <v>215</v>
       </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
         <v>216</v>
       </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>812</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88">
+        <v>81</v>
+      </c>
+      <c r="C88" t="s">
         <v>217</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>215</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
         <v>216</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>813</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89">
+        <v>81</v>
+      </c>
+      <c r="C89" t="s">
         <v>218</v>
       </c>
-      <c r="C89" t="s">
+      <c r="D89" t="s">
         <v>215</v>
       </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
         <v>216</v>
       </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>814</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90">
+        <v>81</v>
+      </c>
+      <c r="C90" t="s">
         <v>219</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
         <v>215</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>216</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>815</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91">
+        <v>81</v>
+      </c>
+      <c r="C91" t="s">
         <v>220</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>215</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>216</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>816</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92">
+        <v>81</v>
+      </c>
+      <c r="C92" t="s">
         <v>221</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
         <v>215</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
         <v>216</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>817</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93">
+        <v>81</v>
+      </c>
+      <c r="C93" t="s">
         <v>222</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
         <v>215</v>
       </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
         <v>216</v>
       </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>821</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94">
+        <v>82</v>
+      </c>
+      <c r="C94" t="s">
         <v>223</v>
       </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
         <v>215</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
         <v>216</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>822</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95">
+        <v>82</v>
+      </c>
+      <c r="C95" t="s">
         <v>224</v>
       </c>
-      <c r="C95" t="s">
+      <c r="D95" t="s">
         <v>215</v>
       </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
         <v>216</v>
       </c>
-      <c r="E95" t="s">
+      <c r="F95" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>823</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96">
+        <v>82</v>
+      </c>
+      <c r="C96" t="s">
         <v>225</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>215</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
         <v>216</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>824</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97">
+        <v>82</v>
+      </c>
+      <c r="C97" t="s">
         <v>226</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
         <v>215</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
         <v>216</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>825</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98">
+        <v>82</v>
+      </c>
+      <c r="C98" t="s">
         <v>227</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
         <v>215</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
         <v>216</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>826</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99">
+        <v>82</v>
+      </c>
+      <c r="C99" t="s">
         <v>228</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>215</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
         <v>216</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>827</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100">
+        <v>82</v>
+      </c>
+      <c r="C100" t="s">
         <v>229</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>215</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
         <v>216</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>828</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101">
+        <v>82</v>
+      </c>
+      <c r="C101" t="s">
         <v>230</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
         <v>215</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>216</v>
       </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>829</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102">
+        <v>82</v>
+      </c>
+      <c r="C102" t="s">
         <v>231</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>215</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>216</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>831</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103">
+        <v>83</v>
+      </c>
+      <c r="C103" t="s">
         <v>232</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>215</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
         <v>216</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>832</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104">
+        <v>83</v>
+      </c>
+      <c r="C104" t="s">
         <v>233</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
         <v>215</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>216</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>833</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105">
+        <v>83</v>
+      </c>
+      <c r="C105" t="s">
         <v>234</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
         <v>215</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
         <v>216</v>
       </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>911</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106">
+        <v>91</v>
+      </c>
+      <c r="C106" t="s">
         <v>235</v>
-      </c>
-      <c r="C106" t="s">
-        <v>236</v>
       </c>
       <c r="D106" t="s">
         <v>236</v>
       </c>
       <c r="E106" t="s">
+        <v>236</v>
+      </c>
+      <c r="F106" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>912</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107">
+        <v>91</v>
+      </c>
+      <c r="C107" t="s">
         <v>238</v>
-      </c>
-      <c r="C107" t="s">
-        <v>236</v>
       </c>
       <c r="D107" t="s">
         <v>236</v>
       </c>
       <c r="E107" t="s">
+        <v>236</v>
+      </c>
+      <c r="F107" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>913</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108">
+        <v>91</v>
+      </c>
+      <c r="C108" t="s">
         <v>239</v>
-      </c>
-      <c r="C108" t="s">
-        <v>236</v>
       </c>
       <c r="D108" t="s">
         <v>236</v>
       </c>
       <c r="E108" t="s">
+        <v>236</v>
+      </c>
+      <c r="F108" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>914</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109">
+        <v>91</v>
+      </c>
+      <c r="C109" t="s">
         <v>240</v>
-      </c>
-      <c r="C109" t="s">
-        <v>236</v>
       </c>
       <c r="D109" t="s">
         <v>236</v>
       </c>
       <c r="E109" t="s">
+        <v>236</v>
+      </c>
+      <c r="F109" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>915</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110">
+        <v>91</v>
+      </c>
+      <c r="C110" t="s">
         <v>241</v>
-      </c>
-      <c r="C110" t="s">
-        <v>236</v>
       </c>
       <c r="D110" t="s">
         <v>236</v>
       </c>
       <c r="E110" t="s">
+        <v>236</v>
+      </c>
+      <c r="F110" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>916</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111">
+        <v>91</v>
+      </c>
+      <c r="C111" t="s">
         <v>242</v>
-      </c>
-      <c r="C111" t="s">
-        <v>236</v>
       </c>
       <c r="D111" t="s">
         <v>236</v>
       </c>
       <c r="E111" t="s">
+        <v>236</v>
+      </c>
+      <c r="F111" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>921</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112">
+        <v>92</v>
+      </c>
+      <c r="C112" t="s">
         <v>243</v>
-      </c>
-      <c r="C112" t="s">
-        <v>236</v>
       </c>
       <c r="D112" t="s">
         <v>236</v>
       </c>
       <c r="E112" t="s">
+        <v>236</v>
+      </c>
+      <c r="F112" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>931</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113">
+        <v>93</v>
+      </c>
+      <c r="C113" t="s">
         <v>244</v>
-      </c>
-      <c r="C113" t="s">
-        <v>236</v>
       </c>
       <c r="D113" t="s">
         <v>236</v>
       </c>
       <c r="E113" t="s">
+        <v>236</v>
+      </c>
+      <c r="F113" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>932</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114">
+        <v>93</v>
+      </c>
+      <c r="C114" t="s">
         <v>245</v>
-      </c>
-      <c r="C114" t="s">
-        <v>236</v>
       </c>
       <c r="D114" t="s">
         <v>236</v>
       </c>
       <c r="E114" t="s">
+        <v>236</v>
+      </c>
+      <c r="F114" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>933</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115">
+        <v>93</v>
+      </c>
+      <c r="C115" t="s">
         <v>246</v>
-      </c>
-      <c r="C115" t="s">
-        <v>236</v>
       </c>
       <c r="D115" t="s">
         <v>236</v>
       </c>
       <c r="E115" t="s">
+        <v>236</v>
+      </c>
+      <c r="F115" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>996</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116">
+        <v>99</v>
+      </c>
+      <c r="C116" t="s">
         <v>247</v>
-      </c>
-      <c r="C116" t="s">
-        <v>236</v>
       </c>
       <c r="D116" t="s">
         <v>236</v>
       </c>
       <c r="E116" t="s">
+        <v>236</v>
+      </c>
+      <c r="F116" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>997</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117">
+        <v>99</v>
+      </c>
+      <c r="C117" t="s">
         <v>248</v>
-      </c>
-      <c r="C117" t="s">
-        <v>236</v>
       </c>
       <c r="D117" t="s">
         <v>236</v>
       </c>
       <c r="E117" t="s">
+        <v>236</v>
+      </c>
+      <c r="F117" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>998</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118">
+        <v>99</v>
+      </c>
+      <c r="C118" t="s">
         <v>249</v>
-      </c>
-      <c r="C118" t="s">
-        <v>236</v>
       </c>
       <c r="D118" t="s">
         <v>236</v>
       </c>
       <c r="E118" t="s">
+        <v>236</v>
+      </c>
+      <c r="F118" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>999</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119">
+        <v>99</v>
+      </c>
+      <c r="C119" t="s">
         <v>250</v>
-      </c>
-      <c r="C119" t="s">
-        <v>236</v>
       </c>
       <c r="D119" t="s">
         <v>236</v>
       </c>
       <c r="E119" t="s">
+        <v>236</v>
+      </c>
+      <c r="F119" t="s">
         <v>237</v>
       </c>
     </row>

--- a/Data/Excel/NLFS_II/classification_NLFS_II.xlsx
+++ b/Data/Excel/NLFS_II/classification_NLFS_II.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10709"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Formal_Informal_wage\Data\Excel\NLFS_II\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandeepsharma/Desktop/Research/Data Analysis/Formal Informal wage/Formal_Informal_wage/Data/Excel/NLFS_II/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B77DF3-0E9F-4414-8FA2-601703785223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{D76ABD63-D262-CE43-B4D5-6A8AA7A9EFDE}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="26740" windowHeight="12540" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="caste_II" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="361">
   <si>
     <t>value</t>
   </si>
@@ -1075,6 +1075,42 @@
   </si>
   <si>
     <t>two_digit</t>
+  </si>
+  <si>
+    <t>gdp_sector</t>
+  </si>
+  <si>
+    <t>Arts_entertain_other</t>
+  </si>
+  <si>
+    <t>Trade_repair</t>
+  </si>
+  <si>
+    <t>Food_accomodation</t>
+  </si>
+  <si>
+    <t>Transport_storage</t>
+  </si>
+  <si>
+    <t>Info_communication</t>
+  </si>
+  <si>
+    <t>Financial_insurance</t>
+  </si>
+  <si>
+    <t>Adminstrative_support_service</t>
+  </si>
+  <si>
+    <t>Professional_scientific_technical</t>
+  </si>
+  <si>
+    <t>Public_admin_defense</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Health_social_work</t>
   </si>
 </sst>
 </file>
@@ -1434,12 +1470,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D104"/>
-  <sheetFormatPr defaultColWidth="11.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="23.1796875" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1453,7 +1489,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1467,7 +1503,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1481,7 +1517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1495,7 +1531,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1509,7 +1545,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1523,7 +1559,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1537,7 +1573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1551,7 +1587,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1565,7 +1601,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1579,7 +1615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1593,7 +1629,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1607,7 +1643,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1621,7 +1657,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1635,7 +1671,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1649,7 +1685,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1663,7 +1699,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1677,7 +1713,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1691,7 +1727,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1705,7 +1741,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1719,7 +1755,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1733,7 +1769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1747,7 +1783,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1761,7 +1797,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1775,7 +1811,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1789,7 +1825,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1803,7 +1839,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1817,7 +1853,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1831,7 +1867,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1845,7 +1881,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1859,7 +1895,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1873,7 +1909,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1887,7 +1923,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1901,7 +1937,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1915,7 +1951,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1929,7 +1965,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1943,7 +1979,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1957,7 +1993,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1971,7 +2007,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1985,7 +2021,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1999,7 +2035,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2013,7 +2049,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2027,7 +2063,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2041,7 +2077,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2055,7 +2091,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2069,7 +2105,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2083,7 +2119,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2097,7 +2133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2111,7 +2147,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2125,7 +2161,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2139,7 +2175,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2153,7 +2189,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2167,7 +2203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2181,7 +2217,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2195,7 +2231,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2209,7 +2245,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2223,7 +2259,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2237,7 +2273,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2251,7 +2287,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2265,7 +2301,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2279,7 +2315,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2293,7 +2329,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2307,7 +2343,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2321,7 +2357,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2335,7 +2371,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2349,7 +2385,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2363,7 +2399,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2377,7 +2413,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2391,7 +2427,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2405,7 +2441,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2419,7 +2455,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2433,7 +2469,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2447,7 +2483,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2461,7 +2497,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2475,7 +2511,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -2489,7 +2525,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2503,7 +2539,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2517,7 +2553,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -2531,7 +2567,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -2545,7 +2581,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2559,7 +2595,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -2573,7 +2609,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -2587,7 +2623,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2601,7 +2637,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -2615,7 +2651,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -2629,7 +2665,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2643,7 +2679,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -2657,7 +2693,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -2671,7 +2707,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -2685,7 +2721,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -2699,7 +2735,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -2713,7 +2749,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -2727,7 +2763,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -2741,7 +2777,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -2755,7 +2791,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -2769,7 +2805,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -2783,7 +2819,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -2797,7 +2833,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -2811,7 +2847,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -2825,7 +2861,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -2839,7 +2875,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -2853,7 +2889,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -2867,7 +2903,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
@@ -2881,7 +2917,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
@@ -2908,15 +2944,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F119"/>
-  <sheetFormatPr defaultColWidth="11.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="74.26953125" customWidth="1"/>
-    <col min="4" max="4" width="35.7265625" customWidth="1"/>
-    <col min="5" max="5" width="38.453125" customWidth="1"/>
-    <col min="6" max="6" width="20.7265625" customWidth="1"/>
+    <col min="3" max="3" width="74.33203125" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" customWidth="1"/>
+    <col min="5" max="5" width="38.5" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2936,7 +2972,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>11</v>
       </c>
@@ -2956,7 +2992,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>111</v>
       </c>
@@ -2976,7 +3012,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>112</v>
       </c>
@@ -2996,7 +3032,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>114</v>
       </c>
@@ -3016,7 +3052,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>121</v>
       </c>
@@ -3036,7 +3072,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>122</v>
       </c>
@@ -3056,7 +3092,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>123</v>
       </c>
@@ -3076,7 +3112,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>131</v>
       </c>
@@ -3096,7 +3132,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>211</v>
       </c>
@@ -3116,7 +3152,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>212</v>
       </c>
@@ -3136,7 +3172,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>213</v>
       </c>
@@ -3156,7 +3192,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>214</v>
       </c>
@@ -3176,7 +3212,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>221</v>
       </c>
@@ -3196,7 +3232,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>222</v>
       </c>
@@ -3216,7 +3252,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>223</v>
       </c>
@@ -3236,7 +3272,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>231</v>
       </c>
@@ -3256,7 +3292,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>232</v>
       </c>
@@ -3276,7 +3312,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>233</v>
       </c>
@@ -3296,7 +3332,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>234</v>
       </c>
@@ -3316,7 +3352,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>235</v>
       </c>
@@ -3336,7 +3372,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>241</v>
       </c>
@@ -3356,7 +3392,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>242</v>
       </c>
@@ -3376,7 +3412,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>243</v>
       </c>
@@ -3396,7 +3432,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>244</v>
       </c>
@@ -3416,7 +3452,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>245</v>
       </c>
@@ -3436,7 +3472,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>246</v>
       </c>
@@ -3456,7 +3492,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>311</v>
       </c>
@@ -3476,7 +3512,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>312</v>
       </c>
@@ -3496,7 +3532,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>313</v>
       </c>
@@ -3516,7 +3552,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>314</v>
       </c>
@@ -3536,7 +3572,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>315</v>
       </c>
@@ -3556,7 +3592,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>321</v>
       </c>
@@ -3576,7 +3612,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>322</v>
       </c>
@@ -3596,7 +3632,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>323</v>
       </c>
@@ -3616,7 +3652,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>324</v>
       </c>
@@ -3636,7 +3672,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>331</v>
       </c>
@@ -3656,7 +3692,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>332</v>
       </c>
@@ -3676,7 +3712,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>333</v>
       </c>
@@ -3696,7 +3732,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>334</v>
       </c>
@@ -3716,7 +3752,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>341</v>
       </c>
@@ -3736,7 +3772,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>342</v>
       </c>
@@ -3756,7 +3792,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>343</v>
       </c>
@@ -3776,7 +3812,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>344</v>
       </c>
@@ -3796,7 +3832,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>345</v>
       </c>
@@ -3816,7 +3852,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>346</v>
       </c>
@@ -3836,7 +3872,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>347</v>
       </c>
@@ -3856,7 +3892,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>348</v>
       </c>
@@ -3876,7 +3912,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>411</v>
       </c>
@@ -3896,7 +3932,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>412</v>
       </c>
@@ -3916,7 +3952,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>413</v>
       </c>
@@ -3936,7 +3972,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>414</v>
       </c>
@@ -3956,7 +3992,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>419</v>
       </c>
@@ -3976,7 +4012,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>421</v>
       </c>
@@ -3996,7 +4032,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>422</v>
       </c>
@@ -4016,7 +4052,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>511</v>
       </c>
@@ -4036,7 +4072,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>512</v>
       </c>
@@ -4056,7 +4092,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>513</v>
       </c>
@@ -4076,7 +4112,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>514</v>
       </c>
@@ -4096,7 +4132,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>515</v>
       </c>
@@ -4116,7 +4152,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>516</v>
       </c>
@@ -4136,7 +4172,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>521</v>
       </c>
@@ -4156,7 +4192,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>522</v>
       </c>
@@ -4176,7 +4212,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>523</v>
       </c>
@@ -4196,7 +4232,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>611</v>
       </c>
@@ -4216,7 +4252,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>612</v>
       </c>
@@ -4236,7 +4272,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>613</v>
       </c>
@@ -4256,7 +4292,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>614</v>
       </c>
@@ -4276,7 +4312,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>615</v>
       </c>
@@ -4296,7 +4332,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>621</v>
       </c>
@@ -4316,7 +4352,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>711</v>
       </c>
@@ -4336,7 +4372,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>712</v>
       </c>
@@ -4356,7 +4392,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>713</v>
       </c>
@@ -4376,7 +4412,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>714</v>
       </c>
@@ -4396,7 +4432,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>721</v>
       </c>
@@ -4416,7 +4452,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>722</v>
       </c>
@@ -4436,7 +4472,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>723</v>
       </c>
@@ -4456,7 +4492,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>724</v>
       </c>
@@ -4476,7 +4512,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>731</v>
       </c>
@@ -4496,7 +4532,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>732</v>
       </c>
@@ -4516,7 +4552,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>733</v>
       </c>
@@ -4536,7 +4572,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>734</v>
       </c>
@@ -4556,7 +4592,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>741</v>
       </c>
@@ -4576,7 +4612,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>742</v>
       </c>
@@ -4596,7 +4632,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>743</v>
       </c>
@@ -4616,7 +4652,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>744</v>
       </c>
@@ -4636,7 +4672,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>811</v>
       </c>
@@ -4656,7 +4692,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>812</v>
       </c>
@@ -4676,7 +4712,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>813</v>
       </c>
@@ -4696,7 +4732,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>814</v>
       </c>
@@ -4716,7 +4752,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>815</v>
       </c>
@@ -4736,7 +4772,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>816</v>
       </c>
@@ -4756,7 +4792,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>817</v>
       </c>
@@ -4776,7 +4812,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>821</v>
       </c>
@@ -4796,7 +4832,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>822</v>
       </c>
@@ -4816,7 +4852,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>823</v>
       </c>
@@ -4836,7 +4872,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>824</v>
       </c>
@@ -4856,7 +4892,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>825</v>
       </c>
@@ -4876,7 +4912,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>826</v>
       </c>
@@ -4896,7 +4932,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>827</v>
       </c>
@@ -4916,7 +4952,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>828</v>
       </c>
@@ -4936,7 +4972,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>829</v>
       </c>
@@ -4956,7 +4992,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>831</v>
       </c>
@@ -4976,7 +5012,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>832</v>
       </c>
@@ -4996,7 +5032,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>833</v>
       </c>
@@ -5016,7 +5052,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>911</v>
       </c>
@@ -5036,7 +5072,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>912</v>
       </c>
@@ -5056,7 +5092,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>913</v>
       </c>
@@ -5076,7 +5112,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>914</v>
       </c>
@@ -5096,7 +5132,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>915</v>
       </c>
@@ -5116,7 +5152,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>916</v>
       </c>
@@ -5136,7 +5172,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>921</v>
       </c>
@@ -5156,7 +5192,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>931</v>
       </c>
@@ -5176,7 +5212,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>932</v>
       </c>
@@ -5196,7 +5232,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>933</v>
       </c>
@@ -5216,7 +5252,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>996</v>
       </c>
@@ -5236,7 +5272,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>997</v>
       </c>
@@ -5256,7 +5292,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>998</v>
       </c>
@@ -5276,7 +5312,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>999</v>
       </c>
@@ -5309,12 +5345,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="11.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="29.54296875" customWidth="1"/>
+    <col min="2" max="2" width="29.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5328,7 +5364,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5342,7 +5378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5356,7 +5392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5370,7 +5406,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -5384,7 +5420,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -5398,7 +5434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -5412,7 +5448,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -5426,7 +5462,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
@@ -5440,7 +5476,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
@@ -5454,7 +5490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
@@ -5468,7 +5504,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -5482,7 +5518,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
@@ -5496,7 +5532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
@@ -5510,7 +5546,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>13</v>
       </c>
@@ -5524,7 +5560,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>14</v>
       </c>
@@ -5538,7 +5574,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>15</v>
       </c>
@@ -5552,7 +5588,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>16</v>
       </c>
@@ -5566,7 +5602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>17</v>
       </c>
@@ -5580,7 +5616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>99</v>
       </c>
@@ -5606,13 +5642,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C61"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D61"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="115.453125" customWidth="1"/>
+    <col min="2" max="2" width="115.5" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5622,8 +5660,11 @@
       <c r="C1" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5633,8 +5674,11 @@
       <c r="C2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5644,8 +5688,11 @@
       <c r="C3" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>5</v>
       </c>
@@ -5655,8 +5702,11 @@
       <c r="C4" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>10</v>
       </c>
@@ -5666,8 +5716,11 @@
       <c r="C5" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>11</v>
       </c>
@@ -5677,8 +5730,11 @@
       <c r="C6" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D6" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>12</v>
       </c>
@@ -5688,8 +5744,11 @@
       <c r="C7" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>13</v>
       </c>
@@ -5699,8 +5758,11 @@
       <c r="C8" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D8" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>14</v>
       </c>
@@ -5710,8 +5772,11 @@
       <c r="C9" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>15</v>
       </c>
@@ -5721,8 +5786,11 @@
       <c r="C10" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>16</v>
       </c>
@@ -5732,8 +5800,11 @@
       <c r="C11" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D11" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>17</v>
       </c>
@@ -5743,8 +5814,11 @@
       <c r="C12" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D12" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>18</v>
       </c>
@@ -5754,8 +5828,11 @@
       <c r="C13" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D13" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>19</v>
       </c>
@@ -5765,8 +5842,11 @@
       <c r="C14" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D14" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>20</v>
       </c>
@@ -5776,8 +5856,11 @@
       <c r="C15" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D15" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>21</v>
       </c>
@@ -5787,8 +5870,11 @@
       <c r="C16" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D16" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>22</v>
       </c>
@@ -5798,8 +5884,11 @@
       <c r="C17" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D17" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>23</v>
       </c>
@@ -5809,8 +5898,11 @@
       <c r="C18" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D18" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>24</v>
       </c>
@@ -5820,8 +5912,11 @@
       <c r="C19" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D19" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>25</v>
       </c>
@@ -5831,8 +5926,11 @@
       <c r="C20" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D20" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>26</v>
       </c>
@@ -5842,8 +5940,11 @@
       <c r="C21" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D21" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>27</v>
       </c>
@@ -5853,8 +5954,11 @@
       <c r="C22" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D22" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>28</v>
       </c>
@@ -5864,8 +5968,11 @@
       <c r="C23" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D23" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>29</v>
       </c>
@@ -5875,8 +5982,11 @@
       <c r="C24" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D24" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>30</v>
       </c>
@@ -5886,8 +5996,11 @@
       <c r="C25" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D25" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>31</v>
       </c>
@@ -5897,8 +6010,11 @@
       <c r="C26" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D26" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>32</v>
       </c>
@@ -5908,8 +6024,11 @@
       <c r="C27" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D27" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>33</v>
       </c>
@@ -5919,8 +6038,11 @@
       <c r="C28" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D28" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>34</v>
       </c>
@@ -5930,8 +6052,11 @@
       <c r="C29" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D29" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>35</v>
       </c>
@@ -5941,8 +6066,11 @@
       <c r="C30" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D30" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>36</v>
       </c>
@@ -5952,8 +6080,11 @@
       <c r="C31" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D31" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>37</v>
       </c>
@@ -5963,8 +6094,11 @@
       <c r="C32" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D32" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>40</v>
       </c>
@@ -5974,8 +6108,11 @@
       <c r="C33" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D33" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>41</v>
       </c>
@@ -5985,8 +6122,11 @@
       <c r="C34" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D34" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>45</v>
       </c>
@@ -5996,8 +6136,11 @@
       <c r="C35" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D35" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>50</v>
       </c>
@@ -6007,8 +6150,11 @@
       <c r="C36" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D36" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>51</v>
       </c>
@@ -6018,8 +6164,11 @@
       <c r="C37" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D37" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>52</v>
       </c>
@@ -6029,8 +6178,11 @@
       <c r="C38" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D38" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>55</v>
       </c>
@@ -6040,8 +6192,11 @@
       <c r="C39" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D39" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>60</v>
       </c>
@@ -6051,8 +6206,11 @@
       <c r="C40" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D40" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>61</v>
       </c>
@@ -6062,8 +6220,11 @@
       <c r="C41" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D41" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>62</v>
       </c>
@@ -6073,8 +6234,11 @@
       <c r="C42" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D42" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>63</v>
       </c>
@@ -6084,8 +6248,11 @@
       <c r="C43" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D43" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>64</v>
       </c>
@@ -6095,8 +6262,11 @@
       <c r="C44" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D44" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>65</v>
       </c>
@@ -6106,8 +6276,11 @@
       <c r="C45" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D45" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>66</v>
       </c>
@@ -6117,8 +6290,11 @@
       <c r="C46" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D46" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>67</v>
       </c>
@@ -6128,8 +6304,11 @@
       <c r="C47" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D47" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>70</v>
       </c>
@@ -6139,8 +6318,11 @@
       <c r="C48" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D48" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>71</v>
       </c>
@@ -6150,8 +6332,11 @@
       <c r="C49" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D49" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>72</v>
       </c>
@@ -6161,8 +6346,11 @@
       <c r="C50" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D50" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>73</v>
       </c>
@@ -6172,8 +6360,11 @@
       <c r="C51" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D51" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>74</v>
       </c>
@@ -6183,8 +6374,11 @@
       <c r="C52" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D52" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>75</v>
       </c>
@@ -6194,8 +6388,11 @@
       <c r="C53" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D53" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>80</v>
       </c>
@@ -6205,8 +6402,11 @@
       <c r="C54" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D54" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>85</v>
       </c>
@@ -6216,8 +6416,11 @@
       <c r="C55" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D55" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>90</v>
       </c>
@@ -6227,8 +6430,11 @@
       <c r="C56" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D56" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>91</v>
       </c>
@@ -6238,8 +6444,11 @@
       <c r="C57" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D57" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>92</v>
       </c>
@@ -6249,8 +6458,11 @@
       <c r="C58" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D58" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>93</v>
       </c>
@@ -6260,8 +6472,11 @@
       <c r="C59" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D59" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>95</v>
       </c>
@@ -6271,8 +6486,11 @@
       <c r="C60" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D60" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>99</v>
       </c>
@@ -6281,6 +6499,9 @@
       </c>
       <c r="C61" t="s">
         <v>335</v>
+      </c>
+      <c r="D61" t="s">
+        <v>350</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Excel/NLFS_II/classification_NLFS_II.xlsx
+++ b/Data/Excel/NLFS_II/classification_NLFS_II.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandeepsharma/Desktop/Research/Data Analysis/Formal Informal wage/Formal_Informal_wage/Data/Excel/NLFS_II/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{D76ABD63-D262-CE43-B4D5-6A8AA7A9EFDE}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{3275E443-0017-8045-89BD-8F27E3B82DD2}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="26740" windowHeight="12540" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27320" windowHeight="14860" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="caste_II" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="362">
   <si>
     <t>value</t>
   </si>
@@ -1111,6 +1111,9 @@
   </si>
   <si>
     <t>Health_social_work</t>
+  </si>
+  <si>
+    <t>Real_estate</t>
   </si>
 </sst>
 </file>
@@ -6319,7 +6322,7 @@
         <v>317</v>
       </c>
       <c r="D48" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">

--- a/Data/Excel/NLFS_II/classification_NLFS_II.xlsx
+++ b/Data/Excel/NLFS_II/classification_NLFS_II.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandeepsharma/Desktop/Research/Data Analysis/Formal Informal wage/Formal_Informal_wage/Data/Excel/NLFS_II/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandeepsharma/Desktop/Research/Data Analysis/Formal Informal wage/Formal_informal_wage/Data/Excel/NLFS_II/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{3275E443-0017-8045-89BD-8F27E3B82DD2}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{13DB6BC5-F8E8-3B49-B6E3-3C34D2F3B13F}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="27320" windowHeight="14860" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27320" windowHeight="14860" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="caste_II" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="361">
   <si>
     <t>value</t>
   </si>
@@ -673,9 +673,6 @@
   </si>
   <si>
     <t>MINING AND MINERAL-PROCESSING PLANT OPERATORS</t>
-  </si>
-  <si>
-    <t>Plant and machine operators, and assemblers</t>
   </si>
   <si>
     <t>Plant_operator</t>
@@ -2960,7 +2957,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C1" t="s">
         <v>115</v>
@@ -3929,7 +3926,7 @@
         <v>172</v>
       </c>
       <c r="E49" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F49" t="s">
         <v>173</v>
@@ -3949,7 +3946,7 @@
         <v>172</v>
       </c>
       <c r="E50" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F50" t="s">
         <v>173</v>
@@ -3969,7 +3966,7 @@
         <v>172</v>
       </c>
       <c r="E51" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F51" t="s">
         <v>173</v>
@@ -3989,7 +3986,7 @@
         <v>172</v>
       </c>
       <c r="E52" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F52" t="s">
         <v>173</v>
@@ -4009,7 +4006,7 @@
         <v>172</v>
       </c>
       <c r="E53" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F53" t="s">
         <v>173</v>
@@ -4029,7 +4026,7 @@
         <v>172</v>
       </c>
       <c r="E54" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F54" t="s">
         <v>173</v>
@@ -4049,7 +4046,7 @@
         <v>172</v>
       </c>
       <c r="E55" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F55" t="s">
         <v>173</v>
@@ -4069,7 +4066,7 @@
         <v>181</v>
       </c>
       <c r="E56" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F56" t="s">
         <v>173</v>
@@ -4089,7 +4086,7 @@
         <v>181</v>
       </c>
       <c r="E57" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F57" t="s">
         <v>173</v>
@@ -4109,7 +4106,7 @@
         <v>181</v>
       </c>
       <c r="E58" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F58" t="s">
         <v>173</v>
@@ -4129,7 +4126,7 @@
         <v>181</v>
       </c>
       <c r="E59" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F59" t="s">
         <v>173</v>
@@ -4149,7 +4146,7 @@
         <v>181</v>
       </c>
       <c r="E60" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F60" t="s">
         <v>173</v>
@@ -4169,7 +4166,7 @@
         <v>181</v>
       </c>
       <c r="E61" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F61" t="s">
         <v>173</v>
@@ -4189,7 +4186,7 @@
         <v>181</v>
       </c>
       <c r="E62" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F62" t="s">
         <v>173</v>
@@ -4209,7 +4206,7 @@
         <v>181</v>
       </c>
       <c r="E63" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F63" t="s">
         <v>173</v>
@@ -4229,7 +4226,7 @@
         <v>181</v>
       </c>
       <c r="E64" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F64" t="s">
         <v>173</v>
@@ -4249,7 +4246,7 @@
         <v>191</v>
       </c>
       <c r="E65" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F65" t="s">
         <v>173</v>
@@ -4269,7 +4266,7 @@
         <v>191</v>
       </c>
       <c r="E66" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F66" t="s">
         <v>173</v>
@@ -4289,7 +4286,7 @@
         <v>191</v>
       </c>
       <c r="E67" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F67" t="s">
         <v>173</v>
@@ -4309,7 +4306,7 @@
         <v>191</v>
       </c>
       <c r="E68" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F68" t="s">
         <v>173</v>
@@ -4329,7 +4326,7 @@
         <v>191</v>
       </c>
       <c r="E69" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F69" t="s">
         <v>173</v>
@@ -4349,7 +4346,7 @@
         <v>191</v>
       </c>
       <c r="E70" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F70" t="s">
         <v>173</v>
@@ -4369,7 +4366,7 @@
         <v>198</v>
       </c>
       <c r="E71" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F71" t="s">
         <v>173</v>
@@ -4389,7 +4386,7 @@
         <v>198</v>
       </c>
       <c r="E72" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F72" t="s">
         <v>173</v>
@@ -4409,7 +4406,7 @@
         <v>198</v>
       </c>
       <c r="E73" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F73" t="s">
         <v>173</v>
@@ -4429,7 +4426,7 @@
         <v>198</v>
       </c>
       <c r="E74" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F74" t="s">
         <v>173</v>
@@ -4449,7 +4446,7 @@
         <v>198</v>
       </c>
       <c r="E75" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F75" t="s">
         <v>173</v>
@@ -4469,7 +4466,7 @@
         <v>198</v>
       </c>
       <c r="E76" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F76" t="s">
         <v>173</v>
@@ -4489,7 +4486,7 @@
         <v>198</v>
       </c>
       <c r="E77" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F77" t="s">
         <v>173</v>
@@ -4509,7 +4506,7 @@
         <v>198</v>
       </c>
       <c r="E78" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F78" t="s">
         <v>173</v>
@@ -4529,7 +4526,7 @@
         <v>198</v>
       </c>
       <c r="E79" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F79" t="s">
         <v>173</v>
@@ -4549,7 +4546,7 @@
         <v>198</v>
       </c>
       <c r="E80" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F80" t="s">
         <v>173</v>
@@ -4569,7 +4566,7 @@
         <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F81" t="s">
         <v>173</v>
@@ -4589,7 +4586,7 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F82" t="s">
         <v>173</v>
@@ -4609,7 +4606,7 @@
         <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F83" t="s">
         <v>173</v>
@@ -4629,7 +4626,7 @@
         <v>198</v>
       </c>
       <c r="E84" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F84" t="s">
         <v>173</v>
@@ -4649,7 +4646,7 @@
         <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F85" t="s">
         <v>173</v>
@@ -4669,7 +4666,7 @@
         <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F86" t="s">
         <v>173</v>
@@ -4689,7 +4686,7 @@
         <v>215</v>
       </c>
       <c r="E87" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F87" t="s">
         <v>173</v>
@@ -4703,13 +4700,13 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D88" t="s">
         <v>215</v>
       </c>
       <c r="E88" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F88" t="s">
         <v>173</v>
@@ -4723,13 +4720,13 @@
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D89" t="s">
         <v>215</v>
       </c>
       <c r="E89" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F89" t="s">
         <v>173</v>
@@ -4743,13 +4740,13 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D90" t="s">
         <v>215</v>
       </c>
       <c r="E90" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F90" t="s">
         <v>173</v>
@@ -4763,13 +4760,13 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D91" t="s">
         <v>215</v>
       </c>
       <c r="E91" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F91" t="s">
         <v>173</v>
@@ -4783,13 +4780,13 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D92" t="s">
         <v>215</v>
       </c>
       <c r="E92" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F92" t="s">
         <v>173</v>
@@ -4803,13 +4800,13 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D93" t="s">
         <v>215</v>
       </c>
       <c r="E93" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F93" t="s">
         <v>173</v>
@@ -4823,13 +4820,13 @@
         <v>82</v>
       </c>
       <c r="C94" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D94" t="s">
         <v>215</v>
       </c>
       <c r="E94" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F94" t="s">
         <v>173</v>
@@ -4843,13 +4840,13 @@
         <v>82</v>
       </c>
       <c r="C95" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D95" t="s">
         <v>215</v>
       </c>
       <c r="E95" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F95" t="s">
         <v>173</v>
@@ -4863,13 +4860,13 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D96" t="s">
         <v>215</v>
       </c>
       <c r="E96" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F96" t="s">
         <v>173</v>
@@ -4883,13 +4880,13 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D97" t="s">
         <v>215</v>
       </c>
       <c r="E97" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F97" t="s">
         <v>173</v>
@@ -4903,13 +4900,13 @@
         <v>82</v>
       </c>
       <c r="C98" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D98" t="s">
         <v>215</v>
       </c>
       <c r="E98" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F98" t="s">
         <v>173</v>
@@ -4923,13 +4920,13 @@
         <v>82</v>
       </c>
       <c r="C99" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D99" t="s">
         <v>215</v>
       </c>
       <c r="E99" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F99" t="s">
         <v>173</v>
@@ -4943,13 +4940,13 @@
         <v>82</v>
       </c>
       <c r="C100" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D100" t="s">
         <v>215</v>
       </c>
       <c r="E100" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F100" t="s">
         <v>173</v>
@@ -4963,13 +4960,13 @@
         <v>82</v>
       </c>
       <c r="C101" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D101" t="s">
         <v>215</v>
       </c>
       <c r="E101" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F101" t="s">
         <v>173</v>
@@ -4983,13 +4980,13 @@
         <v>82</v>
       </c>
       <c r="C102" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D102" t="s">
         <v>215</v>
       </c>
       <c r="E102" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F102" t="s">
         <v>173</v>
@@ -5003,13 +5000,13 @@
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D103" t="s">
         <v>215</v>
       </c>
       <c r="E103" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F103" t="s">
         <v>173</v>
@@ -5023,13 +5020,13 @@
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D104" t="s">
         <v>215</v>
       </c>
       <c r="E104" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F104" t="s">
         <v>173</v>
@@ -5043,13 +5040,13 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D105" t="s">
         <v>215</v>
       </c>
       <c r="E105" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F105" t="s">
         <v>173</v>
@@ -5063,16 +5060,16 @@
         <v>91</v>
       </c>
       <c r="C106" t="s">
+        <v>234</v>
+      </c>
+      <c r="D106" t="s">
         <v>235</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
+        <v>235</v>
+      </c>
+      <c r="F106" t="s">
         <v>236</v>
-      </c>
-      <c r="E106" t="s">
-        <v>236</v>
-      </c>
-      <c r="F106" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
@@ -5083,16 +5080,16 @@
         <v>91</v>
       </c>
       <c r="C107" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D107" t="s">
+        <v>235</v>
+      </c>
+      <c r="E107" t="s">
+        <v>235</v>
+      </c>
+      <c r="F107" t="s">
         <v>236</v>
-      </c>
-      <c r="E107" t="s">
-        <v>236</v>
-      </c>
-      <c r="F107" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
@@ -5103,16 +5100,16 @@
         <v>91</v>
       </c>
       <c r="C108" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D108" t="s">
+        <v>235</v>
+      </c>
+      <c r="E108" t="s">
+        <v>235</v>
+      </c>
+      <c r="F108" t="s">
         <v>236</v>
-      </c>
-      <c r="E108" t="s">
-        <v>236</v>
-      </c>
-      <c r="F108" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
@@ -5123,16 +5120,16 @@
         <v>91</v>
       </c>
       <c r="C109" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D109" t="s">
+        <v>235</v>
+      </c>
+      <c r="E109" t="s">
+        <v>235</v>
+      </c>
+      <c r="F109" t="s">
         <v>236</v>
-      </c>
-      <c r="E109" t="s">
-        <v>236</v>
-      </c>
-      <c r="F109" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
@@ -5143,16 +5140,16 @@
         <v>91</v>
       </c>
       <c r="C110" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D110" t="s">
+        <v>235</v>
+      </c>
+      <c r="E110" t="s">
+        <v>235</v>
+      </c>
+      <c r="F110" t="s">
         <v>236</v>
-      </c>
-      <c r="E110" t="s">
-        <v>236</v>
-      </c>
-      <c r="F110" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
@@ -5163,16 +5160,16 @@
         <v>91</v>
       </c>
       <c r="C111" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D111" t="s">
+        <v>235</v>
+      </c>
+      <c r="E111" t="s">
+        <v>235</v>
+      </c>
+      <c r="F111" t="s">
         <v>236</v>
-      </c>
-      <c r="E111" t="s">
-        <v>236</v>
-      </c>
-      <c r="F111" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
@@ -5183,16 +5180,16 @@
         <v>92</v>
       </c>
       <c r="C112" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D112" t="s">
+        <v>235</v>
+      </c>
+      <c r="E112" t="s">
+        <v>235</v>
+      </c>
+      <c r="F112" t="s">
         <v>236</v>
-      </c>
-      <c r="E112" t="s">
-        <v>236</v>
-      </c>
-      <c r="F112" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
@@ -5203,16 +5200,16 @@
         <v>93</v>
       </c>
       <c r="C113" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D113" t="s">
+        <v>235</v>
+      </c>
+      <c r="E113" t="s">
+        <v>235</v>
+      </c>
+      <c r="F113" t="s">
         <v>236</v>
-      </c>
-      <c r="E113" t="s">
-        <v>236</v>
-      </c>
-      <c r="F113" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
@@ -5223,16 +5220,16 @@
         <v>93</v>
       </c>
       <c r="C114" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D114" t="s">
+        <v>235</v>
+      </c>
+      <c r="E114" t="s">
+        <v>235</v>
+      </c>
+      <c r="F114" t="s">
         <v>236</v>
-      </c>
-      <c r="E114" t="s">
-        <v>236</v>
-      </c>
-      <c r="F114" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
@@ -5243,16 +5240,16 @@
         <v>93</v>
       </c>
       <c r="C115" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D115" t="s">
+        <v>235</v>
+      </c>
+      <c r="E115" t="s">
+        <v>235</v>
+      </c>
+      <c r="F115" t="s">
         <v>236</v>
-      </c>
-      <c r="E115" t="s">
-        <v>236</v>
-      </c>
-      <c r="F115" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
@@ -5263,16 +5260,16 @@
         <v>99</v>
       </c>
       <c r="C116" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D116" t="s">
+        <v>235</v>
+      </c>
+      <c r="E116" t="s">
+        <v>235</v>
+      </c>
+      <c r="F116" t="s">
         <v>236</v>
-      </c>
-      <c r="E116" t="s">
-        <v>236</v>
-      </c>
-      <c r="F116" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
@@ -5283,16 +5280,16 @@
         <v>99</v>
       </c>
       <c r="C117" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D117" t="s">
+        <v>235</v>
+      </c>
+      <c r="E117" t="s">
+        <v>235</v>
+      </c>
+      <c r="F117" t="s">
         <v>236</v>
-      </c>
-      <c r="E117" t="s">
-        <v>236</v>
-      </c>
-      <c r="F117" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
@@ -5303,16 +5300,16 @@
         <v>99</v>
       </c>
       <c r="C118" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D118" t="s">
+        <v>235</v>
+      </c>
+      <c r="E118" t="s">
+        <v>235</v>
+      </c>
+      <c r="F118" t="s">
         <v>236</v>
-      </c>
-      <c r="E118" t="s">
-        <v>236</v>
-      </c>
-      <c r="F118" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
@@ -5323,16 +5320,16 @@
         <v>99</v>
       </c>
       <c r="C119" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D119" t="s">
+        <v>235</v>
+      </c>
+      <c r="E119" t="s">
+        <v>235</v>
+      </c>
+      <c r="F119" t="s">
         <v>236</v>
-      </c>
-      <c r="E119" t="s">
-        <v>236</v>
-      </c>
-      <c r="F119" t="s">
-        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -5361,10 +5358,10 @@
         <v>115</v>
       </c>
       <c r="C1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1" t="s">
         <v>251</v>
-      </c>
-      <c r="D1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -5372,10 +5369,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" t="s">
         <v>253</v>
-      </c>
-      <c r="C2" t="s">
-        <v>254</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -5386,10 +5383,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -5400,10 +5397,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -5414,10 +5411,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -5428,10 +5425,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -5442,10 +5439,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>258</v>
+      </c>
+      <c r="C7" t="s">
         <v>259</v>
-      </c>
-      <c r="C7" t="s">
-        <v>260</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -5456,10 +5453,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -5470,10 +5467,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -5484,10 +5481,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -5498,10 +5495,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -5512,10 +5509,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C12" t="s">
         <v>265</v>
-      </c>
-      <c r="C12" t="s">
-        <v>266</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -5526,10 +5523,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D13">
         <v>11</v>
@@ -5540,10 +5537,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>267</v>
+      </c>
+      <c r="C14" t="s">
         <v>268</v>
-      </c>
-      <c r="C14" t="s">
-        <v>269</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -5554,10 +5551,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
+        <v>269</v>
+      </c>
+      <c r="C15" t="s">
         <v>270</v>
-      </c>
-      <c r="C15" t="s">
-        <v>271</v>
       </c>
       <c r="D15">
         <v>17</v>
@@ -5568,10 +5565,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>271</v>
+      </c>
+      <c r="C16" t="s">
         <v>272</v>
-      </c>
-      <c r="C16" t="s">
-        <v>273</v>
       </c>
       <c r="D16">
         <v>19</v>
@@ -5582,10 +5579,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C17" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D17">
         <v>13</v>
@@ -5596,10 +5593,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -5610,10 +5607,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
+        <v>275</v>
+      </c>
+      <c r="C19" t="s">
         <v>276</v>
-      </c>
-      <c r="C19" t="s">
-        <v>277</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -5624,10 +5621,10 @@
         <v>99</v>
       </c>
       <c r="B20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C20" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -5661,10 +5658,10 @@
         <v>115</v>
       </c>
       <c r="C1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -5672,13 +5669,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C2" t="s">
         <v>279</v>
       </c>
-      <c r="C2" t="s">
-        <v>280</v>
-      </c>
       <c r="D2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -5686,13 +5683,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -5700,13 +5697,13 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -5714,13 +5711,13 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -5728,13 +5725,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -5742,13 +5739,13 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -5756,13 +5753,13 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -5770,13 +5767,13 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -5784,13 +5781,13 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
+        <v>287</v>
+      </c>
+      <c r="C10" t="s">
         <v>288</v>
       </c>
-      <c r="C10" t="s">
-        <v>289</v>
-      </c>
       <c r="D10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -5798,13 +5795,13 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -5812,13 +5809,13 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -5826,13 +5823,13 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -5840,13 +5837,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C14" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D14" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -5854,13 +5851,13 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -5868,13 +5865,13 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C16" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D16" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -5882,13 +5879,13 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -5896,13 +5893,13 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C18" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D18" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -5910,13 +5907,13 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -5924,13 +5921,13 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -5938,13 +5935,13 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -5952,13 +5949,13 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C22" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D22" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -5966,13 +5963,13 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C23" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D23" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -5980,13 +5977,13 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -5994,13 +5991,13 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C25" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D25" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -6008,13 +6005,13 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C26" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -6022,13 +6019,13 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C27" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -6036,13 +6033,13 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -6050,13 +6047,13 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C29" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -6064,13 +6061,13 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C30" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -6078,13 +6075,13 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C31" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D31" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -6092,13 +6089,13 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C32" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D32" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -6106,13 +6103,13 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C33" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D33" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -6120,13 +6117,13 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C34" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D34" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -6134,13 +6131,13 @@
         <v>45</v>
       </c>
       <c r="B35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C35" t="s">
         <v>314</v>
       </c>
-      <c r="C35" t="s">
-        <v>315</v>
-      </c>
       <c r="D35" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -6148,13 +6145,13 @@
         <v>50</v>
       </c>
       <c r="B36" t="s">
+        <v>315</v>
+      </c>
+      <c r="C36" t="s">
         <v>316</v>
       </c>
-      <c r="C36" t="s">
-        <v>317</v>
-      </c>
       <c r="D36" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -6162,13 +6159,13 @@
         <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C37" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D37" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
@@ -6176,13 +6173,13 @@
         <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C38" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D38" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -6190,13 +6187,13 @@
         <v>55</v>
       </c>
       <c r="B39" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C39" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D39" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -6204,13 +6201,13 @@
         <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C40" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D40" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -6218,13 +6215,13 @@
         <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C41" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D41" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -6232,13 +6229,13 @@
         <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C42" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D42" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -6246,13 +6243,13 @@
         <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C43" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D43" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -6260,13 +6257,13 @@
         <v>64</v>
       </c>
       <c r="B44" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C44" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D44" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -6274,13 +6271,13 @@
         <v>65</v>
       </c>
       <c r="B45" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C45" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D45" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -6288,13 +6285,13 @@
         <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C46" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D46" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -6302,13 +6299,13 @@
         <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C47" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D47" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
@@ -6316,13 +6313,13 @@
         <v>70</v>
       </c>
       <c r="B48" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C48" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D48" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -6330,13 +6327,13 @@
         <v>71</v>
       </c>
       <c r="B49" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C49" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D49" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
@@ -6344,13 +6341,13 @@
         <v>72</v>
       </c>
       <c r="B50" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C50" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D50" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
@@ -6358,13 +6355,13 @@
         <v>73</v>
       </c>
       <c r="B51" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C51" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D51" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
@@ -6372,13 +6369,13 @@
         <v>74</v>
       </c>
       <c r="B52" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C52" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D52" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
@@ -6386,13 +6383,13 @@
         <v>75</v>
       </c>
       <c r="B53" t="s">
+        <v>333</v>
+      </c>
+      <c r="C53" t="s">
         <v>334</v>
       </c>
-      <c r="C53" t="s">
-        <v>335</v>
-      </c>
       <c r="D53" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -6400,13 +6397,13 @@
         <v>80</v>
       </c>
       <c r="B54" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C54" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D54" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
@@ -6414,13 +6411,13 @@
         <v>85</v>
       </c>
       <c r="B55" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C55" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D55" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
@@ -6428,13 +6425,13 @@
         <v>90</v>
       </c>
       <c r="B56" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C56" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D56" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -6442,13 +6439,13 @@
         <v>91</v>
       </c>
       <c r="B57" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C57" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D57" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -6456,13 +6453,13 @@
         <v>92</v>
       </c>
       <c r="B58" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C58" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D58" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -6470,13 +6467,13 @@
         <v>93</v>
       </c>
       <c r="B59" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C59" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D59" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -6484,13 +6481,13 @@
         <v>95</v>
       </c>
       <c r="B60" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C60" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D60" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -6498,13 +6495,13 @@
         <v>99</v>
       </c>
       <c r="B61" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C61" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D61" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
